--- a/psychopy_exp_files/sequences/localizer_conditions_things-meg_mixed_5cat_03.xlsx
+++ b/psychopy_exp_files/sequences/localizer_conditions_things-meg_mixed_5cat_03.xlsx
@@ -930,7 +930,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1116,12 +1116,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>boat\boat_05.png</t>
+          <t>sailboat\sailboat_05.png</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -1856,12 +1856,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>boat\boat_11.png</t>
+          <t>sailboat\sailboat_11.png</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>boat\boat_08.png</t>
+          <t>sailboat\sailboat_08.png</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>boat\boat_01.png</t>
+          <t>sailboat\sailboat_01.png</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>boat\boat_04.png</t>
+          <t>sailboat\sailboat_04.png</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>boat\boat_02.png</t>
+          <t>sailboat\sailboat_02.png</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>boat\boat_10.png</t>
+          <t>sailboat\sailboat_10.png</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>boat\boat_06.png</t>
+          <t>sailboat\sailboat_06.png</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>boat\boat_12.png</t>
+          <t>sailboat\sailboat_12.png</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>boat\boat_13.png</t>
+          <t>sailboat\sailboat_13.png</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -7975,12 +7975,12 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>boat\boat_09.png</t>
+          <t>sailboat\sailboat_09.png</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -8341,12 +8341,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>boat\boat_07.png</t>
+          <t>sailboat\sailboat_07.png</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>boat\boat_11.png</t>
+          <t>sailboat\sailboat_11.png</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>boat\boat_03.png</t>
+          <t>sailboat\sailboat_03.png</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9197,7 +9197,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -9211,12 +9211,12 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>boat\boat_10.png</t>
+          <t>sailboat\sailboat_10.png</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -10264,12 +10264,12 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>boat\boat_09.png</t>
+          <t>sailboat\sailboat_09.png</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -11309,12 +11309,12 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>boat\boat_04.png</t>
+          <t>sailboat\sailboat_04.png</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -11730,7 +11730,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>boat\boat_01.png</t>
+          <t>sailboat\sailboat_01.png</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -11860,7 +11860,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>boat\boat_02.png</t>
+          <t>sailboat\sailboat_02.png</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -12118,12 +12118,12 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>boat\boat_08.png</t>
+          <t>sailboat\sailboat_08.png</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -13645,7 +13645,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>boat\boat_07.png</t>
+          <t>sailboat\sailboat_07.png</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -14338,12 +14338,12 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>boat\boat_13.png</t>
+          <t>sailboat\sailboat_13.png</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -14526,7 +14526,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -14637,7 +14637,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -14651,12 +14651,12 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>boat\boat_05.png</t>
+          <t>sailboat\sailboat_05.png</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -15316,7 +15316,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -15330,12 +15330,12 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>boat\boat_12.png</t>
+          <t>sailboat\sailboat_12.png</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -15812,7 +15812,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -15826,12 +15826,12 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>boat\boat_06.png</t>
+          <t>sailboat\sailboat_06.png</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -16422,7 +16422,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -16436,12 +16436,12 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>boat\boat_04.png</t>
+          <t>sailboat\sailboat_04.png</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -17101,7 +17101,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -17115,7 +17115,7 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>boat\boat_03.png</t>
+          <t>sailboat\sailboat_03.png</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -17918,7 +17918,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -17932,12 +17932,12 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>boat\boat_09.png</t>
+          <t>sailboat\sailboat_09.png</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -18603,12 +18603,12 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>boat\boat_11.png</t>
+          <t>sailboat\sailboat_11.png</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -18963,7 +18963,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -18977,12 +18977,12 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>boat\boat_13.png</t>
+          <t>sailboat\sailboat_13.png</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -19656,12 +19656,12 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>boat\boat_12.png</t>
+          <t>sailboat\sailboat_12.png</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -20518,7 +20518,7 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>boat\boat_10.png</t>
+          <t>sailboat\sailboat_10.png</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -20695,7 +20695,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -20709,12 +20709,12 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>boat\boat_03.png</t>
+          <t>sailboat\sailboat_03.png</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -20878,7 +20878,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -20892,12 +20892,12 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>boat\boat_05.png</t>
+          <t>sailboat\sailboat_05.png</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -21984,7 +21984,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G349" t="n">
@@ -21998,12 +21998,12 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>boat\boat_08.png</t>
+          <t>sailboat\sailboat_08.png</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
@@ -22297,7 +22297,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G354" t="n">
@@ -22311,12 +22311,12 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>boat\boat_06.png</t>
+          <t>sailboat\sailboat_06.png</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G357" t="n">
@@ -22494,12 +22494,12 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>boat\boat_02.png</t>
+          <t>sailboat\sailboat_02.png</t>
         </is>
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L357" t="inlineStr">
@@ -22793,7 +22793,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G362" t="n">
@@ -22807,12 +22807,12 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>boat\boat_01.png</t>
+          <t>sailboat\sailboat_01.png</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -23228,7 +23228,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G369" t="n">
@@ -23242,12 +23242,12 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>boat\boat_05.png</t>
+          <t>sailboat\sailboat_05.png</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -24769,7 +24769,7 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G394" t="n">
@@ -24783,12 +24783,12 @@
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>boat\boat_07.png</t>
+          <t>sailboat\sailboat_07.png</t>
         </is>
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L394" t="inlineStr">
@@ -25440,7 +25440,7 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G405" t="n">
@@ -25454,12 +25454,12 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>boat\boat_09.png</t>
+          <t>sailboat\sailboat_09.png</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -26058,7 +26058,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G415" t="n">
@@ -26072,12 +26072,12 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>boat\boat_02.png</t>
+          <t>sailboat\sailboat_02.png</t>
         </is>
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L415" t="inlineStr">
@@ -26729,7 +26729,7 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G426" t="n">
@@ -26743,12 +26743,12 @@
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>boat\boat_08.png</t>
+          <t>sailboat\sailboat_08.png</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
@@ -27347,7 +27347,7 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G436" t="n">
@@ -27361,7 +27361,7 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>boat\boat_13.png</t>
+          <t>sailboat\sailboat_13.png</t>
         </is>
       </c>
       <c r="K436" t="inlineStr">
@@ -27599,7 +27599,7 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G440" t="n">
@@ -27613,12 +27613,12 @@
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>boat\boat_10.png</t>
+          <t>sailboat\sailboat_10.png</t>
         </is>
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L440" t="inlineStr">
@@ -28339,7 +28339,7 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G452" t="n">
@@ -28353,12 +28353,12 @@
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>boat\boat_07.png</t>
+          <t>sailboat\sailboat_07.png</t>
         </is>
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L452" t="inlineStr">
@@ -28461,7 +28461,7 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G454" t="n">
@@ -28475,12 +28475,12 @@
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>boat\boat_01.png</t>
+          <t>sailboat\sailboat_01.png</t>
         </is>
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L454" t="inlineStr">
@@ -29697,7 +29697,7 @@
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G474" t="n">
@@ -29711,12 +29711,12 @@
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>boat\boat_06.png</t>
+          <t>sailboat\sailboat_06.png</t>
         </is>
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L474" t="inlineStr">
@@ -30315,7 +30315,7 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G484" t="n">
@@ -30329,12 +30329,12 @@
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>boat\boat_12.png</t>
+          <t>sailboat\sailboat_12.png</t>
         </is>
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L484" t="inlineStr">
@@ -30559,7 +30559,7 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G488" t="n">
@@ -30573,12 +30573,12 @@
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>boat\boat_03.png</t>
+          <t>sailboat\sailboat_03.png</t>
         </is>
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
@@ -30761,7 +30761,7 @@
       </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L491" t="inlineStr">
@@ -31604,7 +31604,7 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G505" t="n">
@@ -31618,12 +31618,12 @@
       </c>
       <c r="J505" t="inlineStr">
         <is>
-          <t>boat\boat_08.png</t>
+          <t>sailboat\sailboat_08.png</t>
         </is>
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L505" t="inlineStr">
@@ -32344,7 +32344,7 @@
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G517" t="n">
@@ -32358,12 +32358,12 @@
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>boat\boat_11.png</t>
+          <t>sailboat\sailboat_11.png</t>
         </is>
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L517" t="inlineStr">
@@ -33389,7 +33389,7 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G534" t="n">
@@ -33403,12 +33403,12 @@
       </c>
       <c r="J534" t="inlineStr">
         <is>
-          <t>boat\boat_03.png</t>
+          <t>sailboat\sailboat_03.png</t>
         </is>
       </c>
       <c r="K534" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L534" t="inlineStr">
@@ -33946,7 +33946,7 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G543" t="n">
@@ -33960,7 +33960,7 @@
       </c>
       <c r="J543" t="inlineStr">
         <is>
-          <t>boat\boat_04.png</t>
+          <t>sailboat\sailboat_04.png</t>
         </is>
       </c>
       <c r="K543" t="inlineStr">
@@ -34259,7 +34259,7 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G548" t="n">
@@ -34273,12 +34273,12 @@
       </c>
       <c r="J548" t="inlineStr">
         <is>
-          <t>boat\boat_10.png</t>
+          <t>sailboat\sailboat_10.png</t>
         </is>
       </c>
       <c r="K548" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L548" t="inlineStr">
@@ -35365,7 +35365,7 @@
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G566" t="n">
@@ -35379,12 +35379,12 @@
       </c>
       <c r="J566" t="inlineStr">
         <is>
-          <t>boat\boat_12.png</t>
+          <t>sailboat\sailboat_12.png</t>
         </is>
       </c>
       <c r="K566" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L566" t="inlineStr">
@@ -35617,7 +35617,7 @@
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G570" t="n">
@@ -35631,12 +35631,12 @@
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>boat\boat_11.png</t>
+          <t>sailboat\sailboat_11.png</t>
         </is>
       </c>
       <c r="K570" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L570" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G579" t="n">
@@ -36180,12 +36180,12 @@
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>boat\boat_09.png</t>
+          <t>sailboat\sailboat_09.png</t>
         </is>
       </c>
       <c r="K579" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L579" t="inlineStr">
@@ -36540,7 +36540,7 @@
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G585" t="n">
@@ -36554,12 +36554,12 @@
       </c>
       <c r="J585" t="inlineStr">
         <is>
-          <t>boat\boat_01.png</t>
+          <t>sailboat\sailboat_01.png</t>
         </is>
       </c>
       <c r="K585" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L585" t="inlineStr">
@@ -36723,7 +36723,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G588" t="n">
@@ -36737,12 +36737,12 @@
       </c>
       <c r="J588" t="inlineStr">
         <is>
-          <t>boat\boat_04.png</t>
+          <t>sailboat\sailboat_04.png</t>
         </is>
       </c>
       <c r="K588" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L588" t="inlineStr">
@@ -38447,7 +38447,7 @@
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G616" t="n">
@@ -38461,12 +38461,12 @@
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>boat\boat_07.png</t>
+          <t>sailboat\sailboat_07.png</t>
         </is>
       </c>
       <c r="K616" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L616" t="inlineStr">
@@ -38649,7 +38649,7 @@
       </c>
       <c r="K619" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L619" t="inlineStr">
@@ -38760,7 +38760,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G621" t="n">
@@ -38774,12 +38774,12 @@
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>boat\boat_02.png</t>
+          <t>sailboat\sailboat_02.png</t>
         </is>
       </c>
       <c r="K621" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L621" t="inlineStr">
@@ -39370,7 +39370,7 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G631" t="n">
@@ -39384,12 +39384,12 @@
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>boat\boat_13.png</t>
+          <t>sailboat\sailboat_13.png</t>
         </is>
       </c>
       <c r="K631" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L631" t="inlineStr">
@@ -40057,7 +40057,7 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G642" t="n">
@@ -40071,12 +40071,12 @@
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>boat\boat_05.png</t>
+          <t>sailboat\sailboat_05.png</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L642" t="inlineStr">
@@ -40728,7 +40728,7 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="G653" t="n">
@@ -40742,12 +40742,12 @@
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>boat\boat_06.png</t>
+          <t>sailboat\sailboat_06.png</t>
         </is>
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>sailboat</t>
         </is>
       </c>
       <c r="L653" t="inlineStr">
